--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="564">
   <si>
     <t xml:space="preserve">ISO/IEC 27001:2022 Annex A και Microsoft 365: checklist</t>
   </si>
@@ -323,6 +323,9 @@
     <t xml:space="preserve">Συμμετοχές σε φορείς και κοινότητες, συνδρομές ενημέρωσης.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 ή Microsoft 365 E5 (Threat analytics)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.5.7</t>
   </si>
   <si>
@@ -333,13 +336,13 @@
 Συλλογή και ανάλυση πληροφοριών για απειλές.</t>
   </si>
   <si>
-    <t xml:space="preserve">Threat analytics στο Microsoft Defender XDR, με το ποια assets του οργανισμού εκθέτει κάθε απειλή. Threat context στο Defender Vulnerability Management. Microsoft Defender Threat Intelligence για έρευνα σε βάθος.</t>
+    <t xml:space="preserve">Threat analytics στο Microsoft Defender XDR, με το ποια assets του οργανισμού εκθέτει κάθε απειλή. Threat context στο Defender Vulnerability Management. Intel explorer στο Defender portal για έρευνα σε βάθος.</t>
   </si>
   <si>
     <t xml:space="preserve">Threat analytics: αναφορές με εκτεθειμένα assets και ενέργειες. Καταγραφή του πώς αξιοποιήθηκαν.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender Threat Intelligence (premium)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 ή Microsoft 365 E5 (Threat analytics, Defender Vulnerability Management)</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
@@ -375,7 +378,7 @@
     <t xml:space="preserve">Εξαγωγές device και software inventory. Μητρώο αγαθών με ιδιοκτήτη.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender for IoT (για τα αγαθά OT)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (software inventory), Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery), Microsoft 365 E5 ή Microsoft Purview Suite (Content explorer), Microsoft Defender for IoT (για τα αγαθά OT)</t>
   </si>
   <si>
     <t xml:space="preserve">Ο ορισμός ιδιοκτήτη ανά αγαθό δεν καλύπτεται από προϊόντα Microsoft. Τα αγαθά OT δεν καλύπτονται από το Microsoft 365.</t>
@@ -450,7 +453,7 @@
     <t xml:space="preserve">Purview: label policies και Activity explorer με τη χρήση των labels.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 ή Microsoft Purview Information Protection (auto-labeling)</t>
+    <t xml:space="preserve">Microsoft 365 E5, Microsoft Purview Suite ή Microsoft 365 E5 Information Protection and Governance (auto-labeling). Microsoft 365 E5 ή Microsoft Purview Suite (Activity explorer)</t>
   </si>
   <si>
     <t xml:space="preserve">A.5.14</t>
@@ -570,6 +573,9 @@
     <t xml:space="preserve">Μητρώο προμηθευτών. Defender for Cloud Apps: κατάλογος εφαρμογών σε χρήση.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery). Microsoft Entra ID P2 ή Microsoft Entra ID Governance (access reviews)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Η αξιολόγηση των προμηθευτών είναι οργανωτικό μέτρο.</t>
   </si>
   <si>
@@ -607,6 +613,9 @@
   </si>
   <si>
     <t xml:space="preserve">Defender for Cloud Apps: risk score και κατάσταση sanctioned ή unsanctioned. Entra ID: enterprise applications και consent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
@@ -627,9 +636,6 @@
     <t xml:space="preserve">Message center: ιστορικό αλλαγών. Αποτελέσματα access reviews. Πρακτικά ανασκόπησης προμηθευτών.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID P2 ή Microsoft Entra ID Governance (access reviews)</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/generally-available/cross-tenant-message-recall-exchange-online/
 https://thecybersec.gr/posts/entra-tenant-governance-ga/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/</t>
@@ -648,7 +654,7 @@
     <t xml:space="preserve">Πολιτική χρήσης cloud. Defender for Cloud Apps: discovered apps. Secure Score.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender for Cloud (για Azure και multicloud)</t>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery). Microsoft Defender for Cloud (για Azure και multicloud)</t>
   </si>
   <si>
     <t xml:space="preserve">Η στρατηγική εξόδου από έναν πάροχο είναι οργανωτικό έγγραφο.</t>
@@ -690,6 +696,9 @@
     <t xml:space="preserve">Defender XDR: ιστορικό incidents με classification και determination.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft 365 E5 ή Microsoft Defender Suite (automated investigation and response)</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/</t>
@@ -708,6 +717,9 @@
     <t xml:space="preserve">Action center: ιστορικό ενεργειών αποκατάστασης με χρόνο και υπεύθυνο.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft 365 E5 ή Microsoft Defender Suite (automated investigation and response, ενέργειες σε email με Defender for Office 365 Plan 2). Η απομόνωση συσκευής υπάρχει και στο Defender for Endpoint Plan 1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.5.27</t>
   </si>
   <si>
@@ -721,6 +733,9 @@
     <t xml:space="preserve">Εκθέσεις post-incident review. Αλλαγές σε detection rules ή πολιτικές που προέκυψαν.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Η ανασκόπηση μετά το περιστατικό είναι οργανωτική διαδικασία.</t>
   </si>
   <si>
@@ -737,7 +752,7 @@
     <t xml:space="preserve">Εξαγωγές audit log και advanced hunting. eDiscovery: cases και holds.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 (Purview Audit Premium, eDiscovery Premium)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (investigation package, live response, advanced hunting). Microsoft 365 E5 μόνο αν χρειάζονται Purview Audit Premium ή eDiscovery Premium.</t>
   </si>
   <si>
     <t xml:space="preserve">Ελέγξτε τη διατήρηση των logs πριν τη χρειαστείτε.</t>
@@ -799,7 +814,7 @@
     <t xml:space="preserve">Μητρώο νομικών απαιτήσεων. Compliance Manager: assessments και βαθμολογία.</t>
   </si>
   <si>
-    <t xml:space="preserve">Compliance Manager premium assessments (ανάλογα με το template και την άδεια)</t>
+    <t xml:space="preserve">Τα templates NIS2 Directive, ISO/IEC 27001:2022 και EU GDPR είναι premium. Το Microsoft 365 E5 περιλαμβάνει τρία premium templates χωρίς χρέωση. Με Microsoft 365 E3 αγοράζονται χωριστά.</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
@@ -822,6 +837,9 @@
     <t xml:space="preserve">Μητρώο αδειών λογισμικού. Εξαγωγή software inventory.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (software inventory)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.5.33</t>
   </si>
   <si>
@@ -854,7 +872,7 @@
     <t xml:space="preserve">Purview: Content explorer και DLP policies για προσωπικά δεδομένα. Αρχείο δραστηριοτήτων επεξεργασίας.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Priva (ξεχωριστό προϊόν)</t>
+    <t xml:space="preserve">Microsoft Priva (ξεχωριστό προϊόν). Microsoft 365 E5 ή Microsoft Purview Suite (Content explorer)</t>
   </si>
   <si>
     <t xml:space="preserve">Η συμμόρφωση με τον GDPR είναι κυρίως οργανωτική και νομική.</t>
@@ -1343,6 +1361,9 @@
     <t xml:space="preserve">Defender portal: device health και κατάσταση antivirus. Πολιτικές Safe Attachments και Safe Links.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (EDR)</t>
+  </si>
+  <si>
     <t xml:space="preserve">20</t>
   </si>
   <si>
@@ -1364,6 +1385,9 @@
     <t xml:space="preserve">Defender Vulnerability Management: exposure score, Weaknesses, κατάσταση remediation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 ή Microsoft Defender Vulnerability Management Standalone</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.8.9</t>
   </si>
   <si>
@@ -1401,6 +1425,9 @@
     <t xml:space="preserve">Purview: retention policies με ενέργεια διαγραφής, disposition reviews.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft 365 E5 (disposition review)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.8.11</t>
   </si>
   <si>
@@ -1430,7 +1457,7 @@
     <t xml:space="preserve">Purview: DLP policies, alerts και Activity explorer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 (Endpoint DLP, Teams DLP), Microsoft Entra Internet Access (Network Data Security)</t>
+    <t xml:space="preserve">Microsoft 365 E5 (Endpoint DLP, Teams DLP, Network Data Security), Microsoft Entra Internet Access (Network Data Security)</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.13</t>
@@ -1481,7 +1508,7 @@
     <t xml:space="preserve">Purview: audit log search και audit retention policies. Entra ID: diagnostic settings.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 (Purview Audit Premium), Microsoft Sentinel</t>
+    <t xml:space="preserve">Microsoft 365 E5 (Purview Audit Premium), Microsoft Sentinel. Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο)</t>
   </si>
   <si>
     <t xml:space="preserve">Ελέγξτε την προεπιλεγμένη διατήρηση κάθε πηγής.</t>
@@ -1500,7 +1527,7 @@
     <t xml:space="preserve">Defender XDR: incidents και custom detection rules. Entra ID Protection: risk detections.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID P2 (ID Protection), Microsoft Sentinel</t>
+    <t xml:space="preserve">Microsoft Entra ID P2 (ID Protection), Microsoft Sentinel. Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο)</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.17</t>
@@ -1529,7 +1556,7 @@
     <t xml:space="preserve">Intune: πολιτικές App Control και ASR. Αναφορές ανύψωσης δικαιωμάτων.</t>
   </si>
   <si>
-    <t xml:space="preserve">Intune Endpoint Privilege Management (πρόσθετο του Intune)</t>
+    <t xml:space="preserve">Intune Endpoint Privilege Management (περιλαμβάνεται στο Microsoft 365 E5 ή αγοράζεται ως πρόσθετο του Intune)</t>
   </si>
   <si>
     <t xml:space="preserve">13, 14</t>
@@ -1568,7 +1595,7 @@
     <t xml:space="preserve">Ρυθμίσεις firewall. Intune: πολιτικές Windows Firewall.</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure Firewall (μόνο για workloads σε Azure)</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access, Microsoft Entra Private Access</t>
   </si>
   <si>
     <t xml:space="preserve">19</t>
@@ -1589,9 +1616,6 @@
   </si>
   <si>
     <t xml:space="preserve">Συμβάσεις και SLA δικτυακών υπηρεσιών. Global Secure Access: traffic forwarding profiles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access, Microsoft Entra Private Access</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
@@ -1645,13 +1669,13 @@
 Κανόνες για την αποτελεσματική χρήση κρυπτογραφίας και τη διαχείριση κλειδιών.</t>
   </si>
   <si>
-    <t xml:space="preserve">BitLocker μέσω Intune. Sensitivity labels με κρυπτογράφηση και Message Encryption στο Purview. TLS στις υπηρεσίες του Microsoft 365. Customer Key για δικά σας κλειδιά.</t>
+    <t xml:space="preserve">BitLocker μέσω Intune. Sensitivity labels με κρυπτογράφηση και Message Encryption στο Purview. TLS στις υπηρεσίες του Microsoft 365. Customer Key για δικά σας κλειδιά. Microsoft Cloud PKI για την έκδοση πιστοποιητικών σε συσκευές.</t>
   </si>
   <si>
     <t xml:space="preserve">Πολιτική κρυπτογραφίας. Intune: encryption report. Purview: labels με encryption.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 (Customer Key), Microsoft Cloud PKI</t>
+    <t xml:space="preserve">Microsoft 365 E5 (Customer Key, Microsoft Cloud PKI). Το Microsoft Cloud PKI διατίθεται και ως πρόσθετο του Intune.</t>
   </si>
   <si>
     <t xml:space="preserve">Οι διακομιστές και οι βάσεις άλλων κατασκευαστών δεν καλύπτονται από προϊόντα Microsoft.</t>
@@ -2852,7 +2876,9 @@
       <c r="H7" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="8"/>
+      <c r="I7" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="J7" s="8"/>
       <c r="K7" s="7"/>
       <c r="L7" s="8"/>
@@ -2864,7 +2890,7 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>5</v>
@@ -2873,29 +2899,29 @@
         <v>63</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
@@ -2905,7 +2931,7 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>5</v>
@@ -2915,7 +2941,7 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>44</v>
@@ -2924,12 +2950,12 @@
         <v>89</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="9"/>
@@ -2938,9 +2964,9 @@
       <c r="P9" s="11"/>
       <c r="Q9" s="10"/>
     </row>
-    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>5</v>
@@ -2950,28 +2976,28 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
@@ -2981,7 +3007,7 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>5</v>
@@ -2991,24 +3017,24 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
@@ -3018,7 +3044,7 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>5</v>
@@ -3028,24 +3054,24 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
@@ -3055,7 +3081,7 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>5</v>
@@ -3065,26 +3091,26 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
@@ -3092,9 +3118,9 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="10"/>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>5</v>
@@ -3104,26 +3130,26 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
@@ -3133,7 +3159,7 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>5</v>
@@ -3143,24 +3169,24 @@
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
@@ -3170,7 +3196,7 @@
     </row>
     <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>5</v>
@@ -3180,26 +3206,26 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
@@ -3209,7 +3235,7 @@
     </row>
     <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>5</v>
@@ -3219,26 +3245,26 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
@@ -3248,7 +3274,7 @@
     </row>
     <row r="18" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>5</v>
@@ -3258,24 +3284,24 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
@@ -3285,7 +3311,7 @@
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>5</v>
@@ -3295,26 +3321,26 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
@@ -3322,9 +3348,9 @@
       <c r="P19" s="11"/>
       <c r="Q19" s="10"/>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>5</v>
@@ -3334,26 +3360,28 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="8"/>
+        <v>170</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="J20" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
@@ -3363,7 +3391,7 @@
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>5</v>
@@ -3373,24 +3401,24 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -3400,7 +3428,7 @@
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>5</v>
@@ -3410,24 +3438,26 @@
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="I22" s="8"/>
+        <v>183</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="J22" s="8"/>
       <c r="K22" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
@@ -3437,7 +3467,7 @@
     </row>
     <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>5</v>
@@ -3447,26 +3477,26 @@
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
@@ -3476,7 +3506,7 @@
     </row>
     <row r="24" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>5</v>
@@ -3485,31 +3515,31 @@
         <v>63</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
@@ -3519,7 +3549,7 @@
     </row>
     <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>5</v>
@@ -3529,16 +3559,16 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -3546,7 +3576,7 @@
         <v>91</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
@@ -3556,7 +3586,7 @@
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>5</v>
@@ -3566,24 +3596,26 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="I26" s="8"/>
+        <v>206</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>207</v>
+      </c>
       <c r="J26" s="8"/>
       <c r="K26" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
@@ -3593,7 +3625,7 @@
     </row>
     <row r="27" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>5</v>
@@ -3603,24 +3635,26 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="I27" s="8"/>
+        <v>212</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="J27" s="8"/>
       <c r="K27" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
@@ -3630,7 +3664,7 @@
     </row>
     <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>5</v>
@@ -3640,26 +3674,28 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="I28" s="8"/>
+        <v>217</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>218</v>
+      </c>
       <c r="J28" s="8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M28" s="9"/>
       <c r="N28" s="10"/>
@@ -3669,7 +3705,7 @@
     </row>
     <row r="29" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>5</v>
@@ -3679,28 +3715,28 @@
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M29" s="9"/>
       <c r="N29" s="10"/>
@@ -3710,7 +3746,7 @@
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>5</v>
@@ -3720,23 +3756,23 @@
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="L30" s="8"/>
       <c r="M30" s="9"/>
@@ -3747,7 +3783,7 @@
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>5</v>
@@ -3756,28 +3792,28 @@
         <v>63</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I31" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="L31" s="8"/>
       <c r="M31" s="9"/>
@@ -3786,9 +3822,9 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>5</v>
@@ -3798,26 +3834,26 @@
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M32" s="9"/>
       <c r="N32" s="10"/>
@@ -3827,7 +3863,7 @@
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>5</v>
@@ -3837,18 +3873,20 @@
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="I33" s="8"/>
+        <v>249</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>250</v>
+      </c>
       <c r="J33" s="8"/>
       <c r="K33" s="7"/>
       <c r="L33" s="8"/>
@@ -3860,7 +3898,7 @@
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>5</v>
@@ -3870,26 +3908,26 @@
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M34" s="9"/>
       <c r="N34" s="10"/>
@@ -3899,7 +3937,7 @@
     </row>
     <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>5</v>
@@ -3909,26 +3947,26 @@
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M35" s="9"/>
       <c r="N35" s="10"/>
@@ -3938,7 +3976,7 @@
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>5</v>
@@ -3948,24 +3986,24 @@
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M36" s="9"/>
       <c r="N36" s="10"/>
@@ -3975,7 +4013,7 @@
     </row>
     <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>5</v>
@@ -3985,24 +4023,24 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M37" s="9"/>
       <c r="N37" s="10"/>
@@ -4012,7 +4050,7 @@
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>5</v>
@@ -4022,16 +4060,16 @@
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -4047,17 +4085,17 @@
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>44</v>
@@ -4066,12 +4104,12 @@
         <v>89</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="7" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="9"/>
@@ -4082,31 +4120,31 @@
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="7" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="9"/>
@@ -4117,38 +4155,38 @@
     </row>
     <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="M41" s="9"/>
       <c r="N41" s="10"/>
@@ -4158,17 +4196,17 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>44</v>
@@ -4177,12 +4215,12 @@
         <v>89</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="7" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="9"/>
@@ -4193,38 +4231,38 @@
     </row>
     <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M43" s="9"/>
       <c r="N43" s="10"/>
@@ -4234,17 +4272,17 @@
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>44</v>
@@ -4253,12 +4291,12 @@
         <v>89</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="7" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="9"/>
@@ -4269,36 +4307,36 @@
     </row>
     <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="J45" s="8"/>
       <c r="K45" s="7" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M45" s="9"/>
       <c r="N45" s="10"/>
@@ -4308,36 +4346,36 @@
     </row>
     <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="M46" s="9"/>
       <c r="N46" s="10"/>
@@ -4347,31 +4385,31 @@
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L47" s="8"/>
       <c r="M47" s="9"/>
@@ -4382,31 +4420,31 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L48" s="8"/>
       <c r="M48" s="9"/>
@@ -4417,31 +4455,31 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="9"/>
@@ -4452,33 +4490,33 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L50" s="8"/>
       <c r="M50" s="9"/>
@@ -4489,31 +4527,31 @@
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
       <c r="K51" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="9"/>
@@ -4524,31 +4562,31 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B52" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L52" s="8"/>
       <c r="M52" s="9"/>
@@ -4559,36 +4597,36 @@
     </row>
     <row r="53" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B53" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="M53" s="9"/>
       <c r="N53" s="10"/>
@@ -4598,31 +4636,31 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B54" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L54" s="8"/>
       <c r="M54" s="9"/>
@@ -4633,34 +4671,34 @@
     </row>
     <row r="55" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B55" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M55" s="9"/>
       <c r="N55" s="10"/>
@@ -4670,38 +4708,38 @@
     </row>
     <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="J56" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L56" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>349</v>
       </c>
       <c r="M56" s="9"/>
       <c r="N56" s="10"/>
@@ -4711,31 +4749,31 @@
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L57" s="8"/>
       <c r="M57" s="9"/>
@@ -4746,31 +4784,31 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L58" s="8"/>
       <c r="M58" s="9"/>
@@ -4781,31 +4819,31 @@
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
       <c r="K59" s="7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L59" s="8"/>
       <c r="M59" s="9"/>
@@ -4816,36 +4854,36 @@
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M60" s="9"/>
       <c r="N60" s="10"/>
@@ -4855,34 +4893,34 @@
     </row>
     <row r="61" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B61" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
       <c r="K61" s="7" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="M61" s="9"/>
       <c r="N61" s="10"/>
@@ -4892,33 +4930,33 @@
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>79</v>
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>81</v>
@@ -4931,34 +4969,34 @@
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="M63" s="9"/>
       <c r="N63" s="10"/>
@@ -4968,33 +5006,33 @@
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L64" s="8"/>
       <c r="M64" s="9"/>
@@ -5005,34 +5043,34 @@
     </row>
     <row r="65" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M65" s="9"/>
       <c r="N65" s="10"/>
@@ -5042,30 +5080,30 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="8"/>
@@ -5077,34 +5115,36 @@
     </row>
     <row r="67" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I67" s="8"/>
+        <v>409</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>410</v>
+      </c>
       <c r="J67" s="8"/>
       <c r="K67" s="7" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M67" s="9"/>
       <c r="N67" s="10"/>
@@ -5114,34 +5154,36 @@
     </row>
     <row r="68" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="I68" s="8"/>
+        <v>416</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>417</v>
+      </c>
       <c r="J68" s="8"/>
       <c r="K68" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M68" s="9"/>
       <c r="N68" s="10"/>
@@ -5151,38 +5193,38 @@
     </row>
     <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="7" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M69" s="9"/>
       <c r="N69" s="10"/>
@@ -5192,36 +5234,38 @@
     </row>
     <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="I70" s="8"/>
+        <v>428</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>429</v>
+      </c>
       <c r="J70" s="8"/>
       <c r="K70" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M70" s="9"/>
       <c r="N70" s="10"/>
@@ -5231,31 +5275,31 @@
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="7"/>
@@ -5266,40 +5310,40 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="10"/>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M72" s="9"/>
       <c r="N72" s="10"/>
@@ -5309,35 +5353,35 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="L73" s="8"/>
       <c r="M73" s="9"/>
@@ -5348,35 +5392,35 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="L74" s="8"/>
       <c r="M74" s="9"/>
@@ -5387,38 +5431,38 @@
     </row>
     <row r="75" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B75" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M75" s="9"/>
       <c r="N75" s="10"/>
@@ -5428,38 +5472,38 @@
     </row>
     <row r="76" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="7" t="s">
         <v>91</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M76" s="9"/>
       <c r="N76" s="10"/>
@@ -5469,26 +5513,26 @@
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
@@ -5502,36 +5546,36 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="7" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="M78" s="9"/>
       <c r="N78" s="10"/>
@@ -5541,34 +5585,34 @@
     </row>
     <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
       <c r="K79" s="7" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="M79" s="9"/>
       <c r="N79" s="10"/>
@@ -5578,36 +5622,36 @@
     </row>
     <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="7" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="M80" s="9"/>
       <c r="N80" s="10"/>
@@ -5617,36 +5661,36 @@
     </row>
     <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="7" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="M81" s="9"/>
       <c r="N81" s="10"/>
@@ -5656,36 +5700,36 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="7" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="M82" s="9"/>
       <c r="N82" s="10"/>
@@ -5695,38 +5739,38 @@
     </row>
     <row r="83" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="7" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="M83" s="9"/>
       <c r="N83" s="10"/>
@@ -5736,38 +5780,38 @@
     </row>
     <row r="84" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="M84" s="9"/>
       <c r="N84" s="10"/>
@@ -5777,36 +5821,36 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="M85" s="9"/>
       <c r="N85" s="10"/>
@@ -5816,31 +5860,31 @@
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="8"/>
       <c r="K86" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L86" s="8"/>
       <c r="M86" s="9"/>
@@ -5851,31 +5895,31 @@
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B87" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
       <c r="K87" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L87" s="8"/>
       <c r="M87" s="9"/>
@@ -5886,38 +5930,38 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="M88" s="9"/>
       <c r="N88" s="10"/>
@@ -5927,33 +5971,33 @@
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="7" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="L89" s="8"/>
       <c r="M89" s="9"/>
@@ -5964,17 +6008,17 @@
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>44</v>
@@ -5983,12 +6027,12 @@
         <v>89</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="8"/>
       <c r="K90" s="7" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="L90" s="8"/>
       <c r="M90" s="9"/>
@@ -5999,33 +6043,33 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B91" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L91" s="8"/>
       <c r="M91" s="9"/>
@@ -6036,36 +6080,36 @@
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B92" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="M92" s="9"/>
       <c r="N92" s="10"/>
@@ -6075,17 +6119,17 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B93" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>44</v>
@@ -6094,12 +6138,12 @@
         <v>89</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
       <c r="K93" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L93" s="8"/>
       <c r="M93" s="9"/>
@@ -6110,36 +6154,36 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B94" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>79</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M94" s="9"/>
       <c r="N94" s="10"/>
@@ -6189,25 +6233,25 @@
         <v>49</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>37</v>
@@ -6254,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$94,A3)</f>
@@ -6290,7 +6334,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$94,A4)</f>
@@ -6326,7 +6370,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$94,A5)</f>
@@ -6360,7 +6404,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">SUM(C2:C5)</f>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="565">
   <si>
     <t xml:space="preserve">ISO/IEC 27001:2022 Annex A και Microsoft 365: checklist</t>
   </si>
@@ -513,7 +513,7 @@
     <t xml:space="preserve">Entra ID: audit logs δημιουργίας και απενεργοποίησης λογαριασμών, ιστορικό lifecycle workflows.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID Governance (lifecycle workflows)</t>
+    <t xml:space="preserve">Microsoft Entra ID Governance (lifecycle workflows· πρόσθετο, περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
@@ -1035,7 +1035,7 @@
     <t xml:space="preserve">Entra ID: πολιτικές Conditional Access. Intune: αναφορές συμμόρφωσης συσκευών.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Private Access</t>
+    <t xml:space="preserve">Microsoft Entra Private Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">13, 19</t>
@@ -1265,6 +1265,9 @@
     <t xml:space="preserve">Intune: αναφορές συμμόρφωσης. Defender for Endpoint: device inventory με κατάσταση onboarding.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το device inventory</t>
+  </si>
+  <si>
     <t xml:space="preserve">14, 20</t>
   </si>
   <si>
@@ -1457,7 +1460,7 @@
     <t xml:space="preserve">Purview: DLP policies, alerts και Activity explorer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft 365 E5 (Endpoint DLP, Teams DLP, Network Data Security), Microsoft Entra Internet Access (Network Data Security)</t>
+    <t xml:space="preserve">Microsoft 365 E5 (Endpoint DLP, Teams DLP, Network Data Security), Microsoft Entra Internet Access (Network Data Security· Microsoft Entra Suite, standalone ή Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">A.8.13</t>
@@ -1595,7 +1598,7 @@
     <t xml:space="preserve">Ρυθμίσεις firewall. Intune: πολιτικές Windows Firewall.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access, Microsoft Entra Private Access</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7), Microsoft Entra Private Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">19</t>
@@ -1651,7 +1654,7 @@
     <t xml:space="preserve">Defender portal: web content filtering policies και web protection report.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">19, 20</t>
@@ -4914,13 +4917,15 @@
       <c r="H61" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="I61" s="8"/>
+      <c r="I61" s="8" t="s">
+        <v>381</v>
+      </c>
       <c r="J61" s="8"/>
       <c r="K61" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M61" s="9"/>
       <c r="N61" s="10"/>
@@ -4930,7 +4935,7 @@
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>8</v>
@@ -4940,16 +4945,16 @@
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>79</v>
@@ -4969,7 +4974,7 @@
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>8</v>
@@ -4979,16 +4984,16 @@
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -4996,7 +5001,7 @@
         <v>148</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M63" s="9"/>
       <c r="N63" s="10"/>
@@ -5006,7 +5011,7 @@
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>8</v>
@@ -5016,19 +5021,19 @@
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="7" t="s">
@@ -5043,7 +5048,7 @@
     </row>
     <row r="65" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>8</v>
@@ -5053,16 +5058,16 @@
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
@@ -5080,7 +5085,7 @@
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>8</v>
@@ -5090,20 +5095,20 @@
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="8"/>
@@ -5115,7 +5120,7 @@
     </row>
     <row r="67" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>8</v>
@@ -5125,26 +5130,26 @@
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M67" s="9"/>
       <c r="N67" s="10"/>
@@ -5154,7 +5159,7 @@
     </row>
     <row r="68" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>8</v>
@@ -5164,19 +5169,19 @@
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="7" t="s">
@@ -5193,7 +5198,7 @@
     </row>
     <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>8</v>
@@ -5205,26 +5210,26 @@
         <v>98</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M69" s="9"/>
       <c r="N69" s="10"/>
@@ -5234,7 +5239,7 @@
     </row>
     <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>8</v>
@@ -5246,19 +5251,19 @@
         <v>98</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="7" t="s">
@@ -5275,7 +5280,7 @@
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>8</v>
@@ -5287,19 +5292,19 @@
         <v>98</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="7"/>
@@ -5310,9 +5315,9 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="10"/>
     </row>
-    <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>8</v>
@@ -5324,19 +5329,19 @@
         <v>98</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="7" t="s">
@@ -5353,7 +5358,7 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>8</v>
@@ -5363,19 +5368,19 @@
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>238</v>
@@ -5392,7 +5397,7 @@
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>8</v>
@@ -5402,22 +5407,22 @@
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K74" s="7" t="s">
         <v>232</v>
@@ -5431,7 +5436,7 @@
     </row>
     <row r="75" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B75" s="7" t="n">
         <v>8</v>
@@ -5441,22 +5446,22 @@
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>91</v>
@@ -5472,7 +5477,7 @@
     </row>
     <row r="76" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>8</v>
@@ -5484,19 +5489,19 @@
         <v>98</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="7" t="s">
@@ -5513,7 +5518,7 @@
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>8</v>
@@ -5523,16 +5528,16 @@
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
@@ -5546,7 +5551,7 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>8</v>
@@ -5556,26 +5561,26 @@
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M78" s="9"/>
       <c r="N78" s="10"/>
@@ -5585,7 +5590,7 @@
     </row>
     <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>8</v>
@@ -5595,24 +5600,24 @@
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
       <c r="K79" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M79" s="9"/>
       <c r="N79" s="10"/>
@@ -5620,9 +5625,9 @@
       <c r="P79" s="11"/>
       <c r="Q79" s="10"/>
     </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>8</v>
@@ -5632,26 +5637,26 @@
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M80" s="9"/>
       <c r="N80" s="10"/>
@@ -5659,9 +5664,9 @@
       <c r="P80" s="11"/>
       <c r="Q80" s="10"/>
     </row>
-    <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>8</v>
@@ -5671,26 +5676,26 @@
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M81" s="9"/>
       <c r="N81" s="10"/>
@@ -5700,7 +5705,7 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>8</v>
@@ -5710,26 +5715,26 @@
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>311</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M82" s="9"/>
       <c r="N82" s="10"/>
@@ -5739,7 +5744,7 @@
     </row>
     <row r="83" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>8</v>
@@ -5751,26 +5756,26 @@
         <v>98</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M83" s="9"/>
       <c r="N83" s="10"/>
@@ -5780,7 +5785,7 @@
     </row>
     <row r="84" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>8</v>
@@ -5790,28 +5795,28 @@
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K84" s="7" t="s">
         <v>141</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M84" s="9"/>
       <c r="N84" s="10"/>
@@ -5821,7 +5826,7 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>8</v>
@@ -5831,26 +5836,26 @@
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="7" t="s">
         <v>108</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M85" s="9"/>
       <c r="N85" s="10"/>
@@ -5860,7 +5865,7 @@
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>8</v>
@@ -5870,16 +5875,16 @@
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="8"/>
@@ -5895,7 +5900,7 @@
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B87" s="7" t="n">
         <v>8</v>
@@ -5905,16 +5910,16 @@
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
@@ -5930,7 +5935,7 @@
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>8</v>
@@ -5942,26 +5947,26 @@
         <v>98</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="7" t="s">
         <v>108</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M88" s="9"/>
       <c r="N88" s="10"/>
@@ -5971,7 +5976,7 @@
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>8</v>
@@ -5981,23 +5986,23 @@
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L89" s="8"/>
       <c r="M89" s="9"/>
@@ -6008,7 +6013,7 @@
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>8</v>
@@ -6018,7 +6023,7 @@
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>44</v>
@@ -6027,12 +6032,12 @@
         <v>89</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="8"/>
       <c r="K90" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L90" s="8"/>
       <c r="M90" s="9"/>
@@ -6043,7 +6048,7 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B91" s="7" t="n">
         <v>8</v>
@@ -6053,19 +6058,19 @@
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="7" t="s">
@@ -6080,7 +6085,7 @@
     </row>
     <row r="92" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B92" s="7" t="n">
         <v>8</v>
@@ -6090,26 +6095,26 @@
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M92" s="9"/>
       <c r="N92" s="10"/>
@@ -6119,7 +6124,7 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B93" s="7" t="n">
         <v>8</v>
@@ -6129,7 +6134,7 @@
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>44</v>
@@ -6138,7 +6143,7 @@
         <v>89</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
@@ -6154,7 +6159,7 @@
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B94" s="7" t="n">
         <v>8</v>
@@ -6164,16 +6169,16 @@
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>79</v>
@@ -6233,25 +6238,25 @@
         <v>49</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>37</v>
@@ -6404,7 +6409,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">SUM(C2:C5)</f>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -2388,7 +2388,8 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
-https://thecybersec.gr/posts/teams-security-detection-report/</t>
+https://thecybersec.gr/posts/teams-security-detection-report/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="M26" s="26" t="n"/>
@@ -2448,7 +2449,8 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
-https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="M27" s="26" t="n"/>
@@ -4657,7 +4659,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-oikogeneia-praktikos-odigos/
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="M67" s="26" t="n"/>
@@ -4959,7 +4962,8 @@
       </c>
       <c r="L72" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
+          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="M72" s="26" t="n"/>
@@ -5139,7 +5143,8 @@
         <is>
           <t>https://thecybersec.gr/posts/new-features/defender-for-identity-health-issue-missing-windows-events/
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
-https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/</t>
+https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/</t>
         </is>
       </c>
       <c r="M75" s="26" t="n"/>
@@ -5203,7 +5208,9 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
-https://thecybersec.gr/posts/teams-security-detection-report/</t>
+https://thecybersec.gr/posts/teams-security-detection-report/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="M76" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,11 @@
       <c r="L41" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
-https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/</t>
+https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/kouiz-phishing/</t>
         </is>
       </c>
       <c r="M41" s="26" t="n"/>
@@ -4660,7 +4664,8 @@
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/</t>
         </is>
       </c>
       <c r="M67" s="26" t="n"/>
@@ -5611,7 +5616,8 @@
           <t>https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-3-internet-access-profile/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-2-microsoft-traffic-profile/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/</t>
         </is>
       </c>
       <c r="M83" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M26" s="26" t="n"/>
@@ -2450,7 +2451,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M27" s="26" t="n"/>
@@ -4387,7 +4389,8 @@
       <c r="L62" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M62" s="26" t="n"/>
@@ -5149,7 +5152,8 @@
           <t>https://thecybersec.gr/posts/new-features/defender-for-identity-health-issue-missing-windows-events/
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
-https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/</t>
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M75" s="26" t="n"/>
@@ -5215,7 +5219,8 @@
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="M76" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -1452,7 +1452,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/microsoft-defender-oikogeneia-praktikos-odigos/
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M10" s="26" t="n"/>
@@ -1506,7 +1507,8 @@
       </c>
       <c r="L11" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
+          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M11" s="26" t="n"/>
@@ -1967,7 +1969,8 @@
         <is>
           <t>https://thecybersec.gr/posts/previews/ad-group-enforcement-cloud-sync/
 https://thecybersec.gr/posts/entra-tenant-governance-ga/
-https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M19" s="26" t="n"/>
@@ -2029,7 +2032,8 @@
       </c>
       <c r="L20" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M20" s="26" t="n"/>
@@ -2272,7 +2276,8 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
-https://thecybersec.gr/posts/gsa-mcp-firewall/</t>
+https://thecybersec.gr/posts/gsa-mcp-firewall/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M24" s="26" t="n"/>
@@ -4971,7 +4976,8 @@
       <c r="L72" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M72" s="26" t="n"/>
@@ -5220,7 +5226,8 @@
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="M76" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -1005,8 +1005,9 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/</t>
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="M2" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
 https://thecybersec.gr/mitroo-politikon/</t>
         </is>
@@ -2396,7 +2396,8 @@
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="M26" s="26" t="n"/>
@@ -2458,7 +2459,8 @@
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="M27" s="26" t="n"/>
@@ -5160,7 +5162,8 @@
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="M75" s="26" t="n"/>
@@ -5228,7 +5231,8 @@
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="M76" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,8 @@
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
-https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="M26" s="26" t="n"/>
@@ -3538,7 +3539,8 @@
       <c r="L46" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
-https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/</t>
+https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="M46" s="26" t="n"/>
@@ -4676,7 +4678,8 @@
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="M67" s="26" t="n"/>

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,8 @@
       </c>
       <c r="L18" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
         </is>
@@ -4563,7 +4564,8 @@
       </c>
       <c r="L65" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
         </is>
@@ -5228,7 +5230,8 @@
       </c>
       <c r="L76" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/

--- a/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
+++ b/static/downloads/iso-27001-2022-annex-a-microsoft-365-checklist.xlsx
@@ -1908,7 +1908,8 @@
       </c>
       <c r="L18" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
@@ -4564,7 +4565,8 @@
       </c>
       <c r="L65" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
@@ -5230,7 +5232,8 @@
       </c>
       <c r="L76" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
